--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0029.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0029.xlsx
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Utterance of Marvels</t>
+          <t>Lời Huyền Diệu</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Utterance of Marvels</t>
+          <t>Lời Huyền Diệu</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Beginning of a World</t>
+          <t>Khởi Nguyên Của Một Thế Giới</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Silent Glacier</t>
+          <t>Băng Giá Vô Thanh</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Loaded and Chambered</t>
+          <t>Đã nạp đạn và sẵn sàng</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Until Không One Listens</t>
+          <t>Cho Đến Khi Không Còn Ai Lắng Nghe</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Cuối Cùng Cũng Daybreak</t>
+          <t>Cuối Cùng Cũng Bình Minh</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Wooly Nhỏ, Cuộc Phiêu Lưu Lớn</t>
+          <t>Cừu Nhỏ, Đại Phiêu Lưu</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Trở về của Trái Tim Hoang Dã</t>
+          <t>Trở Về Của Trái Tim Hoang Dã</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Những Lối Rẽ Giữa Các Vì Sao</t>
+          <t>Những Ngả Đường Giữa Các Vì Sao</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Lửa Bất Tử</t>
+          <t>Lửa Bất Diệt</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Bản Chất Thật</t>
+          <t>Bản Lĩnh Thật</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Companion Stories</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Những Lối Rẽ Giữa Các Vì Sao</t>
+          <t>Những Ngả Đường Giữa Các Vì Sao</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Nếu Một Night Rainy Gia Đình</t>
+          <t>Nếu Một Đêm Mưa Gia Đình</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Jinzhou Rising</t>
+          <t>Jinzhou Trỗi Dậy</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Act I</t>
+          <t>Hồi I</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Lời Hứa Là Phải Giữ</t>
+          <t>Lời Hứa Là Sẽ Giao, Bạn Nhé</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Act I</t>
+          <t>Hồi I</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Stygian Lacrimosa</t>
+          <t>Huyết Lệ Stygian</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Bãi Lầy Whining Aix</t>
+          <t>Whining Aix's Mire</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Act I</t>
+          <t>Hồi I</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Hiểm Họa Trong Cuộc Sống Bình Yên</t>
+          <t>Hiểm Họa Ẩn Trong Cuộc Sống Bình Yên</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Act I</t>
+          <t>Hồi I</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Shadow Quá Khứ</t>
+          <t>Bóng Tối Quá Khứ</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Act II</t>
+          <t>Hồi II</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Rừng Tối</t>
+          <t>Dim Forest</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Act I</t>
+          <t>Hồi I</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Viên Ngọc Rồng Huy Hoàng</t>
+          <t>Ngọc Trai Của Loong Vinh Quang</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Act I</t>
+          <t>Hồi I</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Echoing Marche</t>
+          <t>Hành Quân Vang Vọng</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Jinzhou Rising</t>
+          <t>Jinzhou Trỗi Dậy</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Act II</t>
+          <t>Hồi II</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Ngôi Sao Điềm Gở</t>
+          <t>Ngôi Sao U Ám</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Jinzhou Rising</t>
+          <t>Jinzhou Trỗi Dậy</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Act III</t>
+          <t>Hồi III</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Kiếm Kích</t>
+          <t>Kiếm kích</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Jinzhou Rising</t>
+          <t>Jinzhou Trỗi Dậy</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Act IV</t>
+          <t>Hồi IV</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Giọt Mưa Quay Ngược</t>
+          <t>Quay ngược Giọt Mưa Rơi</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Jinzhou Rising</t>
+          <t>Jinzhou Trỗi Dậy</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Act V</t>
+          <t>Chương V</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Bão Chiến Vĩ Đại</t>
+          <t>Bão Chiến Đại Chiến</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Jinzhou Rising</t>
+          <t>Jinzhou Trỗi Dậy</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Act VI</t>
+          <t>Chương VI</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Tan Băng Ngàn Năm</t>
+          <t>Thời Khắc Tan Băng</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Jinzhou Rising</t>
+          <t>Jinzhou Trỗi Dậy</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Act VII</t>
+          <t>Chương VII</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>To the Shore's End</t>
+          <t>Đến Bến Cuối Bờ</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Jinzhou Rising</t>
+          <t>Jinzhou Trỗi Dậy</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Black Shores I</t>
+          <t>Bờ Đen I</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Act VIII</t>
+          <t>Chương VIII</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Tale of Moontree Lodge</t>
+          <t>Huyền Thoại Lều Trăng</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Tale of Moontree Lodge</t>
+          <t>Huyền Thoại Lều Trăng</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Moon-Chasing Festival</t>
+          <t>Lễ Hội Đuổi Trăng</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>By Moon's Grace</t>
+          <t>Nhờ Ân Huệ của Mặt Trăng</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Moments</t>
+          <t>Khoảnh khắc</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Moments</t>
+          <t>Khoảnh khắc</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Moon-Chasing Festival</t>
+          <t>Lễ Hội Đuổi Trăng</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>By Moon's Grace</t>
+          <t>Nhờ Ân Huệ của Mặt Trăng</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Cho đến khi Night Dài kết thúc.</t>
+          <t>Cho đến khi Đêm Dài kết thúc.</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Cho đến khi Night Dài kết thúc.</t>
+          <t>Cho đến khi Đêm Dài kết thúc.</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Mê Cung Giấc Mộng</t>
+          <t>Mê Cung Somnium</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Fishing Adventure</t>
+          <t>Cuộc Phiêu Lưu Câu Cá</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Ông Già và Cá Voi</t>
+          <t>Lão Già và Cá Voi</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Riccioli Voyage Log</t>
+          <t>Nhật Ký Hành Trình Riccioli</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Fishing Adventure</t>
+          <t>Cuộc Phiêu Lưu Câu Cá</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Island Encounters</t>
+          <t>Những Cuộc Gặp Gỡ Trên Đảo</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Riccioli Voyage Log</t>
+          <t>Nhật Ký Hành Trình Riccioli</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Act I</t>
+          <t>Hồi I</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Tĩnh lặng như chiếc lá rơi</t>
+          <t>Lặng Như Lá Rơi</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Golden Anthem</t>
+          <t>Khúc Ca Hoàng Kim</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Mùa Hè Của Bạn Sẽ Không Tàn Phai</t>
+          <t>Mùa Hè Của Ngươi Sẽ Không Bao Giờ Tàn Úa</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Mùa Hè Của Bạn Sẽ Không Tàn Phai</t>
+          <t>Mùa Hè Của Ngươi Sẽ Không Bao Giờ Tàn Úa</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>SOL3 Awakening</t>
+          <t>SOL3 Thức Tỉnh</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Quests</t>
+          <t>Nhiệm vụ</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Quests</t>
+          <t>Nhiệm vụ</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Main Quests</t>
+          <t>Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Main Quests</t>
+          <t>Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Test Task</t>
+          <t>Nhiệm vụ thử nghiệm</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Side Quests</t>
+          <t>Nhiệm Vụ Phụ</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Side Quests</t>
+          <t>Nhiệm Vụ Phụ</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Companion Stories</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Companion Stories</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Tutorial Quests</t>
+          <t>Nhiệm Vụ Hướng Dẫn</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Tutorial Quests</t>
+          <t>Nhiệm Vụ Hướng Dẫn</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Exploration Quests</t>
+          <t>Nhiệm Vụ Thám Hiểm</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Exploration Quests</t>
+          <t>Nhiệm Vụ Thám Hiểm</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Event Quests</t>
+          <t>Nhiệm Vụ Sự Kiện</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Event Quests</t>
+          <t>Nhiệm Vụ Sự Kiện</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>A photo of Camellya</t>
+          <t>Bức ảnh Camellya</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>A photo of Camellya 2</t>
+          <t>Bức ảnh Camellya 2</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>A photo of Camellya 3</t>
+          <t>Bức ảnh Camellya 3</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>"Modunasha: New"</t>
+          <t>"Modunasha: Khúc Mới"</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Huanglong News</t>
+          <t>Tin tức Huanglong</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Nghiên cứu Memo A038</t>
+          <t>Biên Bản Nghiên Cứu A038</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Nghiên cứu Memo A038</t>
+          <t>Biên Bản Nghiên Cứu A038</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Loại: Log Thí nghiệm</t>
+          <t>Loại: Nhật ký Thí nghiệm</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Nghiên cứu Memo: A038</t>
+          <t>Biên Bản Nghiên Cứu: A038</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Memo Recording: A038</t>
+          <t>Bản ghi nhớ: A038</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>A Childish Sketch</t>
+          <t>Bức Vẽ Ngây Thơ</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Memo Covered in Blood Stains</t>
+          <t>Bản ghi nhớ vấy đầy vết máu</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Hastily Written Nghiên cứu Ghi chú</t>
+          <t>Ghi Chép Nghiên Cứu Viết Vội</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>A Message From Yinlin</t>
+          <t>Tin Nhắn Từ Yinlin</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>The Séance Society</t>
+          <t>Hội Thông Linh</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Anonymous Message</t>
+          <t>Tin nhắn ẩn danh</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Archive</t>
+          <t>Lưu Trữ</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Tattered Poster</t>
+          <t>Tấm Áp Phích Rách Nát</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Song KU-Tiền</t>
+          <t>Khúc Ca KU-Tiền</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Thực Đơn Quán Tea Hoa Anh Đào</t>
+          <t>Thực Đơn Quán Trà Hoa Anh Đào</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Port Bay Hôm nay</t>
+          <t>Tin Tức Cảng Hôm Nay</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Fragments of Distant Memories</t>
+          <t>Mảnh ký ức xa xăm</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>"Song Trở Về Giấc Mơ III: Lá Đá Nước Mắt"</t>
+          <t>"Khúc Ca Trở Về Giấc Mơ III: Lá Đá Nước Mắt"</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Radio Recording</t>
+          <t>Bản Ghi Âm Đài</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Tattered Booklet</t>
+          <t>Cuốn Sổ Tả Tơi</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>power system notes</t>
+          <t>ghi chú hệ thống năng lượng</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>A Photograph Stained with Blood</t>
+          <t>Bức Ảnh Đẫm Máu</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>A Photograph Covered with Scratches</t>
+          <t>Bức Ảnh Đầy Vết Xước</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>A Brand New Photograph</t>
+          <t>Một Tấm Ảnh Mới Chụp</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Unknown Master's Journal</t>
+          <t>Nhật ký của một bậc thầy vô danh</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Tattered Personal Memo</t>
+          <t>Bản Ghi Nhớ Cá Nhân Rách Nát</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Aircraft Accident Report</t>
+          <t>Báo Cáo Tai Nạn Máy Bay</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Jinzhou Folklore Journal</t>
+          <t>Biên Niên Ký Văn Hóa Dân Gian Jinzhou</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Nghiên Cứu về Echo ở Huanglong</t>
+          <t>Nghiên Cứu về Linh Thú ở Huanglong</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Lo, Lo, Lollo Logistics!</t>
+          <t>Này, này, Lollo Logistics đây!</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Untitled Family Letters</t>
+          <t>Những lá thư gia đình vô đề</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Strange Messages</t>
+          <t>Những Tin Nhắn Kỳ Lạ</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Dim Forest Survey Đội Diary</t>
+          <t>Nhật ký Đội Khảo sát Rừng Âm U</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>History of Huanglong Reconstruction</t>
+          <t>Lịch sử Tái thiết Huanglong</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Loong Bun Ticket</t>
+          <t>Vé Bánh Lồng Đèn Rồng</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Secret Diary - I</t>
+          <t>Nhật Ký Bí Mật - Phần I</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Secret Diary - II</t>
+          <t>Nhật Ký Bí Mật - Phần II</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Paintings under restoration</t>
+          <t>Tranh đang phục chế</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Restoration of records</t>
+          <t>Khôi phục dữ liệu</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Restoration Không. 171</t>
+          <t>Nhiệm Vụ Phục Hồi Số 171</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Restoration Không. 281</t>
+          <t>Nhiệm Vụ Phục Hồi Số 281</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>"Fatherly Love"</t>
+          <t>"Tình phụ tử"</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>"Friendship"</t>
+          <t>"Tình bạn"</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>"Divergence"</t>
+          <t>"Sự Phân Kỳ"</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>"Separation"</t>
+          <t>"Ly Biệt"</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>"Different Ways"</t>
+          <t>"Những Con Đường Khác Biệt"</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Environmental Assessment Mô-đun</t>
+          <t>Mô-đun Đánh giá Môi trường</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Environmental Assessment Mô-đun</t>
+          <t>Mô-đun Đánh giá Môi trường</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Environmental Assessment Mô-đun</t>
+          <t>Mô-đun Đánh giá Môi trường</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Phỏng Vấn Đường Phố Cơ Quan Tin Tức Jinzhou: Tại Sao Gọi Là Tiger's Maw?</t>
+          <t>Phỏng Vấn Đường Phố Cơ Quan Tin Tức Jinzhou: Tại Sao Gọi Là Hàm Hổ?</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Thông báo Kiểm Tra Định Kỳ Xe Vận Tải Hàng Năm</t>
+          <t>Thông Báo Kiểm Tra Định Kỳ Xe Vận Tải Hàng Năm</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Nhật Ký Đội Thăm Dò Hazy Depths I</t>
+          <t>Nhật Ký Đội Thăm Dò Vực Sương Mù I</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Nhật Ký Đội Thăm Dò Hazy Depths II</t>
+          <t>Nhật Ký Đội Thăm Dò Vực Sương Mù II</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Nhật Ký Đội Thăm Dò Hazy Depths III</t>
+          <t>Nhật Ký Đội Thăm Dò Vực Sương Mù III</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>A Joke</t>
+          <t>Chuyện đùa thôi</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Bản Ghi Chat tìm thấy trong Thiết bị Đầu Cuối</t>
+          <t>Bản Ghi Trò Chuyện tìm thấy trong Thiết bị Đầu Cuối</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Equipment Maintenance Log</t>
+          <t>Nhật Ký Bảo Trì Trang Bị</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Engineer's Log</t>
+          <t>Nhật Ký Kỹ Sư</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Warnings for Liquid Tanks</t>
+          <t>Cảnh báo về Bình Chứa Chất Lỏng</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>A Miner's Search Record</t>
+          <t>Bản Ghi Chép Tìm Kiếm Của Thợ Mỏ</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Tune of Rocks</t>
+          <t>Giai Điệu Đá</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>WANTED</t>
+          <t>TUYÊN BỐ TRUY NÃ</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Uncle Hong's Diary I</t>
+          <t>Nhật Ký Bác Hồng I</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Uncle Hong's Diary II</t>
+          <t>Nhật Ký Bác Hồng II</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>AL XXXX Cloudy</t>
+          <t>AL XXXX Trời nhiều mây</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Experiment Report</t>
+          <t>Báo Cáo Thí Nghiệm</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Maosan's Diary</t>
+          <t>Nhật ký Maosan</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Gousi's Ghi chú</t>
+          <t>Ghi Chú Của Gousi</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Popular Hero Play Recommendations</t>
+          <t>Gợi ý Vở kịch Anh hùng Được Yêu thích</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Returning Dreams Sound Material Cửa hàng</t>
+          <t>Kho Vật Liệu Âm Thanh Giấc Mơ Trở Về</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Thông báo on Safety Production</t>
+          <t>Thông Báo Về An Toàn Sản Xuất</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Work Report</t>
+          <t>Báo Cáo Công Việc</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Knell Garden</t>
+          <t>Vườn Knell</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Knell Recording</t>
+          <t>Bản ghi Tiếng Chuông Tang Lễ</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Service Record</t>
+          <t>Hồ Sơ Dịch Vụ</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Viewer Bình luận</t>
+          <t>Bình luận người xem</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Lost and Found</t>
+          <t>Đồ Thất Lạc</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Lollo Logistics Recruitment Thông báo</t>
+          <t>Thông Báo Tuyển Dụng Lollo Logistics</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Huaxu Academy Academic Lecture Schedule</t>
+          <t>Lịch diễn thuyết Học thuật Học viện Huaxu</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Liuxian Teahouse</t>
+          <t>Quán Trà Lục Hiền</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Shiyu's Letter</t>
+          <t>Lá thư của Shiyu</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Shiyu's Letter</t>
+          <t>Lá thư của Shiyu</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Memorandum for Newcomer Exiles</t>
+          <t>Bản ghi nhớ cho những kẻ lưu đày mới</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Obsolete Road Sign</t>
+          <t>Biển Báo Lỗi Thời</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Lost Signs</t>
+          <t>Dấu Hiệu Lạc Mất</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Rhymes of the Olden Days</t>
+          <t>Những Vần Thơ Cổ Xưa</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Drainage Hệ thống</t>
+          <t>Hệ Thống Thoát Nước</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Writings on the Wall</t>
+          <t>Những dòng chữ trên tường</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Sea Watch Notes</t>
+          <t>Ghi Chép Quan Sát Biển</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Tattered Paper</t>
+          <t>Mảnh Giấy Rách Nát</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Cách Old Town Được Xây Dựng: Biên Niên Sử Thăng Trầm Của Gang Hội</t>
+          <t>Cách Old Town Được Xây Dựng: Biên Niên Sử Thăng Trầm Của Bang Hội</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Exile's Diary</t>
+          <t>Nhật Ký Lưu Đày</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Electricity Safety Poster</t>
+          <t>Áp Phích An Toàn Điện</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Exile's Monthly Log</t>
+          <t>Báo Cáo Hàng Tháng Của Lưu Đày</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Inscriptions on the Mysterious "Tube"</t>
+          <t>Những Dòng Khắc Trên "Ống" Bí Ẩn</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>electronic note</t>
+          <t>ghi chú điện tử</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>"Cat Tree"</t>
+          <t>"Cây Mèo"</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Survey sinh thái tại Ruins Bị Sóng Tàn Phá</t>
+          <t>Khảo sát sinh thái tại Tàn Tích Bị Sóng Tàn Phá</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>A bag of Scrap Paper</t>
+          <t>Một túi Giấy Vụn</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Door Plate</t>
+          <t>Bảng Cửa</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Wuming Bay Pre-Lament Record 012</t>
+          <t>Bản Ghi Trước Than Thở Wuming Bay 012</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Wuming Bay Pre-Lament Record 090</t>
+          <t>Bản Ghi Trước Than Thở Wuming Bay 090</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Wuming Bay Pre-Lament Record 137</t>
+          <t>Bản Ghi Trước Than Thở Wuming Bay 137</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Wuming Bay Pre-Lament Record 035</t>
+          <t>Bản Ghi Trước Than Thở Wuming Bay 035</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Wuming Bay Pre-Lament Record 104</t>
+          <t>Bản Ghi Trước Than Thở Wuming Bay 104</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Report Nghiên cứu về Thành phần Mist tại Misty Pits</t>
+          <t>Báo cáo Nghiên cứu về Thành phần Sương mù tại Misty Pits</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Report Sự cố tại Ga Tàu</t>
+          <t>Báo cáo Sự cố tại Ga Tàu</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Report Sự kiện Lịch sử tại Ga Tàu này</t>
+          <t>Báo cáo Sự kiện Lịch sử tại Ga Tàu này</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Unknown Signal</t>
+          <t>Tín Hiệu Lạ</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Evacuation Thông báo</t>
+          <t>Thông báo Sơ tán</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Package List</t>
+          <t>Danh sách Gói</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Banyan Tree "Loong's Gaze"</t>
+          <t>Cây Bồ Đề "Long Nhãn"</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Unsigned Diary: I</t>
+          <t>Nhật Ký Không Ký Tên: I</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Unsigned Diary: II</t>
+          <t>Nhật Ký Không Ký Tên: II</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Unsigned Diary: III</t>
+          <t>Nhật Ký Không Ký Tên: III</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Construction Thông báo</t>
+          <t>Thông Báo Xây Dựng</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>BEWARE THE MENACE</t>
+          <t>COI CHỪNG MỐI ĐE DọA</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>The Comfort Inn ~Issue 100~</t>
+          <t>Quán Trọ Ấm Áp ~Số 100~</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Windy Lighthouse Journal</t>
+          <t>Nhật Ký Hải Đăng Gió</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Work Arrangements</t>
+          <t>Sắp Xếp Công Việc</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Chief's Diary</t>
+          <t>Nhật ký của Ông Trưởng</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Researcher's Diary</t>
+          <t>Nhật ký Nhà nghiên cứu</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Jiaping's Diary</t>
+          <t>Nhật Ký của Jiaping</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Temporary Đội's Group Photo</t>
+          <t>Ảnh nhóm tạm thời</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Gulpuff Relay Leaderboard</t>
+          <t>Bảng Xếp Hạng Tiếp Sức Gulpuff</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Tattered Books</t>
+          <t>Những Cuốn Sách Rách Nát</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>[Interact with the Touchpad]</t>
+          <t>Tương tác với Touchpad</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>List of CampPersonnel</t>
+          <t>Danh sách Nhân sự Trại</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>About the Persona</t>
+          <t>Về Persona</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>About Qiao Sheng:</t>
+          <t>Về Qiao Sheng:</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Camp Member Standing:</t>
+          <t>Thành Viên Trại Đang Đứng Gác:</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Code of Conduct</t>
+          <t>Quy Tắc Ứng Xử</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>IOU</t>
+          <t>GIẤY NỢ</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Oh My Magistrate</t>
+          <t>Ôi Ngài Thẩm Phán</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Port Business Advertisement</t>
+          <t>Quảng Cáo Kinh Doanh Cảng</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Dock Routine</t>
+          <t>Quy trình cập bến</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Expressway Bulletin</t>
+          <t>Thông Báo Xa Lộ</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Mẫu đơn xin cấp vật tư</t>
+          <t>Mẫu Đơn Xin Cấp Vật Tư</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Exiles' Slogan</t>
+          <t>Khẩu Hiệu Của Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Jiting's Nghiên cứu Ghi chú</t>
+          <t>Ghi chép Nghiên cứu của Jiting</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Lollo Logistics Forum Post</t>
+          <t>Bài Đăng Diễn Đàn Lollo Logistics</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Fieild Investigation Ghi chú</t>
+          <t>Ghi Chú Điều Tra Hiện Trường</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Experiment Report về Moire Stone</t>
+          <t>Báo Cáo Thí Nghiệm về Moire Stone</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Báo Cáo Khảo Sát Lựa Chọn Địa Điểm Exploration - Phần Một</t>
+          <t>Báo Cáo Khảo Sát Lựa Chọn Địa Điểm Thám Hiểm - Phần Một</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Báo Cáo Khảo Sát Lựa Chọn Địa Điểm Exploration - Phần Hai</t>
+          <t>Báo Cáo Khảo Sát Lựa Chọn Địa Điểm Thám Hiểm - Phần Hai</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Camp Thông báo</t>
+          <t>Thông báo Trại</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Report Điều tra Gorges of Spirits</t>
+          <t>Báo cáo Điều tra Hẻm Núi Linh Hồn</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Seasonal Popular Play Recommendations</t>
+          <t>Gợi Ý Trò Chơi Phổ Biến Theo Mùa</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Bogu's Arbor</t>
+          <t>Vườn Arbor của Bogu</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Thông báo on Safety Production</t>
+          <t>Thông Báo Về An Toàn Sản Xuất</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Work Report</t>
+          <t>Báo Cáo Công Việc</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Knell Square</t>
+          <t>Quảng trường Knell</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>None, lời thoại kích hoạt trong phạm vi.</t>
+          <t>Không có, lời thoại kích hoạt trong phạm vi.</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Liuxian Teahouse</t>
+          <t>Quán Trà Lục Hiền</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Viewer Bình luận</t>
+          <t>Bình luận người xem</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Lost and Found</t>
+          <t>Đồ Thất Lạc</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Lollo Logistics Price List</t>
+          <t>Bảng Giá Lollo Logistics</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Lollo Logistics Recruitment Thông báo</t>
+          <t>Thông Báo Tuyển Dụng Lollo Logistics</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Huaxu Academy Academic Lecture Schedule</t>
+          <t>Lịch diễn thuyết Học thuật Học viện Huaxu</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey 1</t>
+          <t>Khảo Sát Sinh Thái Rừng U Tối 1</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey 2</t>
+          <t>Khảo Sát Sinh Thái Rừng U Tối 2</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey 3</t>
+          <t>Khảo Sát Sinh Thái Rừng U Tối 3</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey 4</t>
+          <t>Khảo Sát Sinh Thái Rừng U Tối 4</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey 5</t>
+          <t>Khảo Sát Sinh Thái Rừng U Tối 5</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Thông báo Board tại Cổng Bắc</t>
+          <t>Bảng Thông Báo tại Cổng Bắc</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Thông báo Board tại ranh giới Thành Phố Guixu và Rừng Âm U</t>
+          <t>Bảng Thông Báo tại ranh giới Thành Phố Guixu và Rừng Âm U</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Thông báo Board trong Rừng Phía Đông</t>
+          <t>Bảng Thông Báo trong Rừng Phía Đông</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey Summary</t>
+          <t>Tổng Kết Khảo Sát Sinh Thái Rừng U Tối</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Wutherium Geographic - Phỏng vấn tại Jinzhou</t>
+          <t>Địa lý Wutherium - Phỏng vấn tại Jinzhou</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Thông báo Kiểm Tra Định Kỳ Xe Vận Tải Hàng Năm</t>
+          <t>Thông Báo Kiểm Tra Định Kỳ Xe Vận Tải Hàng Năm</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Thông báo về Hiện Tượng Bất Thường của "Discord Ngủ Đông" Dưới Mỏ</t>
+          <t>Thông Báo về Hiện Tượng Bất Thường của "Tacet Discord Ngủ Đông" Dưới Mỏ</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Nhật Ký Đội Thăm Dò Hazy Depths I</t>
+          <t>Nhật Ký Đội Thăm Dò Vực Sương Mù I</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Nhật Ký Đội Thăm Dò Hazy Depths II</t>
+          <t>Nhật Ký Đội Thăm Dò Vực Sương Mù II</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Nhật Ký Đội Thăm Dò Hazy Depths III</t>
+          <t>Nhật Ký Đội Thăm Dò Vực Sương Mù III</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>A Pun</t>
+          <t>Một Câu Nói Đùa</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Bản Ghi Chat tìm thấy trong Thiết bị Đầu Cuối</t>
+          <t>Bản Ghi Trò Chuyện tìm thấy trong Thiết bị Đầu Cuối</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Equipment maintenance records</t>
+          <t>Hồ sơ bảo trì trang bị</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Engineer's Ghi chú</t>
+          <t>Ghi chú của Kỹ sư</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Bản Record Search Của Thợ Mỏ</t>
+          <t>Bản Ghi Chép Tìm Kiếm Của Thợ Mỏ</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Tune of Rocks</t>
+          <t>Giai Điệu Đá</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Unknown Signal</t>
+          <t>Tín Hiệu Lạ</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>[EMERGENCY EVACUATION NOTICE]</t>
+          <t>[THÔNG BÁO SƠ TÁN KHẨN CẤP]</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>[Packing List]</t>
+          <t>["Danh Sách Đóng Gói"]</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Ancient Tree "Loong's Gaze"</t>
+          <t>Cây cổ "Long Nhãn"</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Indistinct Carvings</t>
+          <t>Những hình khắc mờ nhạt</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>BEWARE THE MENACE</t>
+          <t>COI CHỪNG MỐI ĐE DọA</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Courier Monthly</t>
+          <t>Người đưa tin hàng tháng</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Bridging Project [Experiment #2068]</t>
+          <t>Dự Án Kết Nối [Thí nghiệm #2068]</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Nghiên cứu Memo-C2068</t>
+          <t>Biên Bản Nghiên Cứu-C2068</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>A Person's Diary</t>
+          <t>Nhật Ký Của Một Người</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Report Công tác Thám hiểm</t>
+          <t>Báo cáo Công tác Thám hiểm</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Camp Thông báo</t>
+          <t>Thông báo Trại</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Experiment Report về Moire Stone</t>
+          <t>Báo Cáo Thí Nghiệm về Moire Stone</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Report trận chiến Discord - Gorges of Spirits</t>
+          <t>Báo cáo trận chiến Tacet Discord - Hẻm Núi Linh Hồn</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Report Điều tra Gorges of Spirits</t>
+          <t>Báo cáo Điều tra Hẻm Núi Linh Hồn</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Battlefield Record 6010: Autumn</t>
+          <t>Biên bản chiến trường 6010: Mùa thu</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Battlefield Record 6010: 91.7 Highland Contest</t>
+          <t>Biên bản chiến trường 6010: Cuộc chiến Cao nguyên 91.7</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Battlefield Record 6010: Reorganization</t>
+          <t>Hồ Sơ Chiến Trường 6010: Tái Tổ Chức</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Battlefield Record 6010: Setting Off Again</t>
+          <t>Hồ Sơ Chiến Trường 6010: Lại Lên Đường</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Sea of Flames Safety Rules</t>
+          <t>Quy Tắc An Toàn Tại Biển Lửa</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Time Footnote·IX</t>
+          <t>Chú Thích Thời Gian·IX</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Time Footnote·X</t>
+          <t>Chú Thích Thời Gian·X</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Time Footnote·XI</t>
+          <t>Chú Thích Thời Gian·XI</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Time Footnote·XII</t>
+          <t>Chú Thích Thời Gian·XII</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Time Footnote·XIII</t>
+          <t>Chú Thích Thời Gian·XIII</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Someone's Diary</t>
+          <t>Nhật Ký Của Ai Đó</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Someone's Diary #2</t>
+          <t>Nhật Ký Của Ai Đó #2</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Port Business Advertisement</t>
+          <t>Quảng Cáo Kinh Doanh Cảng</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Work Log</t>
+          <t>Nhật Ký Công Việc</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Expressway Bulletin</t>
+          <t>Thông Báo Xa Lộ</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Mẫu đơn xin cấp vật tư</t>
+          <t>Mẫu Đơn Xin Cấp Vật Tư</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Exile Slogan</t>
+          <t>Khẩu Hiệu Lưu Đày</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>CSC Laboratory Visit Handbook</t>
+          <t>Sổ Tay Tham Quan Phòng Thí Nghiệm CSC</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Fjord Lighthouse Expedition Handbook</t>
+          <t>Cẩm Nang Thám Hiểm Hải Đăng Fjord</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Lost Cemetery</t>
+          <t>Nghĩa Trang Bị Lãng Quên</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey 1</t>
+          <t>Khảo Sát Sinh Thái Rừng U Tối 1</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey 2</t>
+          <t>Khảo Sát Sinh Thái Rừng U Tối 2</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey 3</t>
+          <t>Khảo Sát Sinh Thái Rừng U Tối 3</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey 4</t>
+          <t>Khảo Sát Sinh Thái Rừng U Tối 4</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey 5</t>
+          <t>Khảo Sát Sinh Thái Rừng U Tối 5</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey Summary</t>
+          <t>Tổng Kết Khảo Sát Sinh Thái Rừng U Tối</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Map Trên Da Thú</t>
+          <t>Bản Đồ Trên Da Thú</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Quy Định An Toàn Vận Chuyển Trại Midnight Ranger</t>
+          <t>Quy Định An Toàn Vận Chuyển Trại Kỵ Sĩ Bóng Đêm</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Báo Cáo Khảo Sát Chất Lượng Nước Mắt Dragon</t>
+          <t>Báo Cáo Khảo Sát Chất Lượng Nước Mắt Rồng</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Unnamed Wish List</t>
+          <t>Danh sách nguyện vọng vô danh</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Restored Thông báo</t>
+          <t>Thông Báo đã khôi phục.</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Old Sketch</t>
+          <t>Bức Phác Họa Cũ</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Communication Record</t>
+          <t>Bản Ghi Liên Lạc</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Log Điều tra: Sự cố Dự án "Kho báu CSC"</t>
+          <t>Nhật ký Điều tra: Sự cố Dự án "Kho báu CSC"</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Somebody's Diary</t>
+          <t>Nhật ký của ai đó</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Nghiên cứu Memo A038</t>
+          <t>Biên Bản Nghiên Cứu A038</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Experiment Memo SY-A038</t>
+          <t>Bản Ghi Chú Thí Nghiệm SY-A038</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Nghiên cứu Memo A038</t>
+          <t>Biên Bản Nghiên Cứu A038</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Nghiên cứu Memo A038</t>
+          <t>Biên Bản Nghiên Cứu A038</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Diary Entry</t>
+          <t>Nhật ký</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Midnight Rangers' Terminal</t>
+          <t>Thiết Bị Đầu Cuối Kỵ Sĩ Bóng Đêm</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Court of Savantae's Data Chip</t>
+          <t>Chip Dữ Liệu Tòa Savantae</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Special Operation Diary D12547</t>
+          <t>Nhật Ký Hoạt Động Đặc Biệt D12547</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>tattered letter 1 (provisional text)</t>
+          <t>lá thư cũ rách nát 1 (văn bản tạm thời)</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>tattered letters 2 (provisional text)</t>
+          <t>những lá thư cũ rách nát 2 (văn bản tạm thời)</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Tattered Letters 3 (provisional text)</t>
+          <t>Những Bức Thư Rách Nát 3 (văn bản tạm thời)</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>"Archive: Discord"</t>
+          <t>"Lưu trữ: Tacet Discord"</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Huaxu Academy, Jinzhou Campus</t>
+          <t>Học viện Huaxu, Cơ sở Jinzhou</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Stone Tablet</t>
+          <t>Bia Đá</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Tattered Diary</t>
+          <t>Nhật Ký Rách Nát</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Grand Library Route Map</t>
+          <t>Bản Đồ Tuyến Đường Thư Viện Hoàng Gia</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Page sách tranh bị rách</t>
+          <t>Trang Sách Tranh Rách</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Torn Page</t>
+          <t>Trang Giấy Rách</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Paper Strip</t>
+          <t>Dải Giấy</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
